--- a/SNTL_APISpec.xlsx
+++ b/SNTL_APISpec.xlsx
@@ -776,7 +776,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>총 API 수: 143개</t>
+          <t>총 API 수: 183개</t>
         </is>
       </c>
     </row>
